--- a/01-INTRO/M02/bus311-intro-m02-l01-market-cap-activity.xlsx
+++ b/01-INTRO/M02/bus311-intro-m02-l01-market-cap-activity.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29712"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{6B3257E2-1813-4564-8427-ADC7C7CAA416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B03D8B4-59AF-4A29-B9A8-1F7BAF5EBD22}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bethanyevittsair2/Documents/GitHub/BUS311-Corporate_Finance/01-INTRO/M02/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAD53D1-4918-B74E-A8D7-F414B2C6E15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ABD960A4-8EF3-4BD1-B1A9-39CB98FE2B11}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{ABD960A4-8EF3-4BD1-B1A9-39CB98FE2B11}"/>
   </bookViews>
   <sheets>
     <sheet name="Class Activity -Instructions" sheetId="2" r:id="rId1"/>
@@ -565,113 +570,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9462B9C2-AE12-44D7-882B-69CE598D7B9B}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.140625" customWidth="1"/>
-    <col min="2" max="2" width="66.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.1640625" customWidth="1"/>
+    <col min="2" max="2" width="66.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>47</v>
       </c>
@@ -684,147 +689,147 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A97B0E5A-6ED0-4E32-A63B-83112D0CFC72}">
   <dimension ref="A1:A28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>41</v>
       </c>
